--- a/tests/testdata/excel/ファイル名/ガ_合成済み.xlsx
+++ b/tests/testdata/excel/ファイル名/ガ_合成済み.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADF3D6D2-34CD-44FE-A29E-7431B90C7EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBF9F324-76E7-4457-8A9E-00C3E5FC6500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{48CB5916-46AD-46B4-B4A5-6026E3033772}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{64F4A1BC-070D-4F34-8A61-2D3B03ED29B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6846B2F8-9208-4D4B-9F8C-267035E4B062}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A07073E-3D0B-4C42-A945-06AC2FD2287A}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
